--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0124.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0124.xlsx
@@ -11106,7 +11106,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Ôi, con cáo ranh này... Giờ biết làm gì với cậu đây?</t>
+          <t>Ôi, con cáo ranh này... Giờ biết làm gì với mày đây?</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Hahaha, được rồi, được rồi. Ta hiểu rồi, ngươi đang ở trạng thái 100%... Chắc ta không cần lo nữa rồi.</t>
+          <t>Hahaha, được rồi, được rồi. Tao hiểu rồi, mày đang ở trạng thái 100%... Chắc tao không cần lo nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>...Cậu nghĩ nó hiểu không? Hay là không?</t>
+          <t>...Mày nghĩ nó hiểu không? Hay là không?</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi, cứ tin ta và để ta lo, được không?</t>
+          <t>Được rồi, được rồi, cứ tin tao và để tao lo, được không?</t>
         </is>
       </c>
     </row>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Cục bông vẫn nhất quyết tặng quà cho ta... Nhưng rồi ta nghĩ, "Thôi kệ nó." Ít ra giờ nó chỉ tặng mấy thứ vô hại.</t>
+          <t>Cục bông vẫn nhất quyết tặng quà cho tao... Nhưng rồi tao nghĩ, "Thôi kệ nó." Ít ra giờ nó chỉ tặng mấy thứ vô hại.</t>
         </is>
       </c>
     </row>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>...Thật lòng, điều ta muốn chỉ là Fluffball được an toàn thôi.</t>
+          <t>...Thật lòng, điều tao muốn chỉ là Fluffball được an toàn thôi.</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Cái này... À, cậu đang nhìn vào một viên dinh dưỡng ép khô xác ướp đấy.</t>
+          <t>Cái này... À, mày đang nhìn vào một viên dinh dưỡng ép khô xác ướp đấy.</t>
         </is>
       </c>
     </row>
@@ -19816,7 +19816,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Xem qua cái này giúp ta được không?</t>
+          <t>Xem qua cái này giúp tao được không?</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Thực ra ta còn mấy con "quái vật" như này ở nhà nữa.</t>
+          <t>Thực ra tao còn mấy con "quái vật" như này ở nhà nữa.</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hôm nay ta thậm chí còn ở nhà suốt, chỉ để chờ bắt được kẻ đã làm điều đó... Nhưng kết quả là chẳng có gì cả!</t>
+          <t>Hôm nay tao thậm chí còn ở nhà suốt, chỉ để chờ bắt được kẻ đã làm điều đó... Nhưng kết quả là chẳng có gì cả!</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27486,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>"Có vẻ vài con Exoswarm lạc vào trong rừng rồi. Ta sẽ đi tìm chúng. Hy vọng chúng vẫn ổn. —Decima"</t>
+          <t>"Có vẻ vài con Exoswarm lạc vào trong rừng rồi. Tao sẽ đi tìm chúng. Hy vọng chúng vẫn ổn. —Decima"</t>
         </is>
       </c>
     </row>
@@ -29826,7 +29826,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Ta muốn chụp thêm vài tấm nữa. Cậu đợi ta ở đây nhé?</t>
+          <t>Tao muốn chụp thêm vài tấm nữa. Cậu đợi tao ở đây nhé?</t>
         </is>
       </c>
     </row>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -30996,7 +30996,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Muốn biết chúng ta đã nói gì không?</t>
+          <t>Muốn biết chúng tao đã nói gì không?</t>
         </is>
       </c>
     </row>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Nhưng sau đó, ta bắt đầu xây nhà ở nơi khác.</t>
+          <t>Nhưng sau đó, tao bắt đầu xây nhà ở nơi khác.</t>
         </is>
       </c>
     </row>
@@ -32426,7 +32426,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Ta có cảm giác như mình đã đánh mất thứ gì đó ở nơi này.</t>
+          <t>Tao có cảm giác như mình đã đánh mất thứ gì đó ở nơi này.</t>
         </is>
       </c>
     </row>
@@ -32881,7 +32881,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Xin chào, cậu là {PlayerName} phải không?</t>
+          <t>Xin chào, bạn là {PlayerName} phải không?</t>
         </is>
       </c>
     </row>
